--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94CD693-1D5E-429B-A46C-27B67E1A9207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1806F9-A7AD-491C-B522-0DCE0D4DD4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_library_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t>库随机权重</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>1010901,1010902,1010903,1010904,1010905,1010906,1010907,1010908,1010909,1010910,905010101,905010202,905010302,905010403,905010503,905010604,905010704,905010805,900010101,900010202,900010302,900010403,900010503,900010604,900010704,900010805</t>
+  </si>
+  <si>
+    <t>800000001,800010101,800010102,800010201,800010202,800010301,800010302,800030101,800030102,800030201,800030202,800100001,800110101,800110102,800110201,800110202,800110301,800110302,800130101,800130102,800130201,800130202,800200001,800210101,800210102,800210201,800210202,800210301,800210302,800230101,800230102,800230201,800230202,801100001,801100101,801100102,801100103,801100201,801100202,801100203,801100301,801100302,801100303,801200001,801200101,801200102,801200103,801200201,801200202,801200203</t>
   </si>
 </sst>
 </file>
@@ -516,7 +519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F2A891-7ADB-4315-87EE-F51F4FB85BA3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -743,6 +746,76 @@
         <v>100</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>201</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>202</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>203</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>204</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>205</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1806F9-A7AD-491C-B522-0DCE0D4DD4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E50EB2B-BBC2-49BC-81CF-7B5AB2C02C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
@@ -96,7 +96,8 @@
     <t>1010901,1010902,1010903,1010904,1010905,1010906,1010907,1010908,1010909,1010910,905010101,905010202,905010302,905010403,905010503,905010604,905010704,905010805,900010101,900010202,900010302,900010403,900010503,900010604,900010704,900010805</t>
   </si>
   <si>
-    <t>800000001,800010101,800010102,800010201,800010202,800010301,800010302,800030101,800030102,800030201,800030202,800100001,800110101,800110102,800110201,800110202,800110301,800110302,800130101,800130102,800130201,800130202,800200001,800210101,800210102,800210201,800210202,800210301,800210302,800230101,800230102,800230201,800230202,801100001,801100101,801100102,801100103,801100201,801100202,801100203,801100301,801100302,801100303,801200001,801200101,801200102,801200103,801200201,801200202,801200203</t>
+    <t>800000001,800010101,800010102,800010201,800010202,800010301,800010302,800030101,800030102,800030201,800030202,800100001,800110101,800110102,800110201,800110202,800110301,800110302,800130101,800130102,800130201,800130202,800200001,800210101,800210102,800210201,800210202,800210301,800210302,800230101,800230102,800230201,800230202,801100001,801100101,801100102,801100103,801100201,801100202,801100203,801100301,801100302,801100303</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -523,7 +524,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="207.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="105.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E50EB2B-BBC2-49BC-81CF-7B5AB2C02C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DCD933-374D-4843-9F3E-2E83DFD6B376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_library_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
   <si>
     <t>库随机权重</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -98,6 +98,9 @@
   <si>
     <t>800000001,800010101,800010102,800010201,800010202,800010301,800010302,800030101,800030102,800030201,800030202,800100001,800110101,800110102,800110201,800110202,800110301,800110302,800130101,800130102,800130201,800130202,800200001,800210101,800210102,800210201,800210202,800210301,800210302,800230101,800230102,800230201,800230202,801100001,801100101,801100102,801100103,801100201,801100202,801100203,801100301,801100302,801100303</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>700000001,700010101,700010102,700010103,700010104,700010105,700010106,700010107,700010108,700100001,700100101,700100102,700100103,700100104,700100105,700100106,700100107,700100108,700200001,700200101,700200102,700200103,700200104,700200105,700200106,700200107,700200108,700400001,700400002,700400003,700400004,700400101,700400102,700400103,700400104</t>
   </si>
 </sst>
 </file>
@@ -520,7 +523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F2A891-7ADB-4315-87EE-F51F4FB85BA3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -817,6 +820,76 @@
         <v>100</v>
       </c>
     </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>301</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>302</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>303</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>304</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
+        <v>305</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DCD933-374D-4843-9F3E-2E83DFD6B376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C198D0-0109-45D1-BCA2-6542E76C8F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_library_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
   <si>
     <t>库随机权重</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -101,6 +101,10 @@
   </si>
   <si>
     <t>700000001,700010101,700010102,700010103,700010104,700010105,700010106,700010107,700010108,700100001,700100101,700100102,700100103,700100104,700100105,700100106,700100107,700100108,700200001,700200101,700200102,700200103,700200104,700200105,700200106,700200107,700200108,700400001,700400002,700400003,700400004,700400101,700400102,700400103,700400104</t>
+  </si>
+  <si>
+    <t>700000001,700010101,700010102,700010112,700010122,700010132,700010103,700010104,700010105,700010106,700010107,700010108,700100001,700100101,700100102,700100112,700100122,700100132,700100103,700100104,700100105,700100106,700100107,700100108,700200001,700200101,700200102,700200112,700200122,700200132,700200103,700200104,700200105,700200106,700200107,700200108,700400001,700400002,700400003,700400004,700400101,700400102,700400103,700400104</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -828,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C198D0-0109-45D1-BCA2-6542E76C8F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B4F5D2-8937-4715-98E5-40730874A588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_library_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
   <si>
     <t>库随机权重</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -98,9 +98,6 @@
   <si>
     <t>800000001,800010101,800010102,800010201,800010202,800010301,800010302,800030101,800030102,800030201,800030202,800100001,800110101,800110102,800110201,800110202,800110301,800110302,800130101,800130102,800130201,800130202,800200001,800210101,800210102,800210201,800210202,800210301,800210302,800230101,800230102,800230201,800230202,801100001,801100101,801100102,801100103,801100201,801100202,801100203,801100301,801100302,801100303</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>700000001,700010101,700010102,700010103,700010104,700010105,700010106,700010107,700010108,700100001,700100101,700100102,700100103,700100104,700100105,700100106,700100107,700100108,700200001,700200101,700200102,700200103,700200104,700200105,700200106,700200107,700200108,700400001,700400002,700400003,700400004,700400101,700400102,700400103,700400104</t>
   </si>
   <si>
     <t>700000001,700010101,700010102,700010112,700010122,700010132,700010103,700010104,700010105,700010106,700010107,700010108,700100001,700100101,700100102,700100112,700100122,700100132,700100103,700100104,700100105,700100106,700100107,700100108,700200001,700200101,700200102,700200112,700200122,700200132,700200103,700200104,700200105,700200106,700200107,700200108,700400001,700400002,700400003,700400004,700400101,700400102,700400103,700400104</t>
@@ -832,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B4F5D2-8937-4715-98E5-40730874A588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE233A0-3339-42A1-AB8E-52661C12E161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_library_v8" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>700000001,700010101,700010102,700010112,700010122,700010132,700010103,700010104,700010105,700010106,700010107,700010108,700100001,700100101,700100102,700100112,700100122,700100132,700100103,700100104,700100105,700100106,700100107,700100108,700200001,700200101,700200102,700200112,700200122,700200132,700200103,700200104,700200105,700200106,700200107,700200108,700400001,700400002,700400003,700400004,700400101,700400102,700400103,700400104</t>
+    <t>700000001,700010101,700010102,700010112,700010122,700010132,700010103,700010104,700010105,700010106,700010107,700010108,700100001,700100101,700100102,700100112,700100122,700100132,700100103,700100104,700100105,700100106,700100107,700100108,700200001,700200101,700200102,700200112,700200122,700200132,700200103,700200104,700200105,700200106,700200107,700200108,700400001,700400002,700400003,700400004,700400101,700400102,700400103,700400104,801100101,801100102,801100103</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE233A0-3339-42A1-AB8E-52661C12E161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A720D193-2185-40BD-B240-B008B2BB4BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_library_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
   <si>
     <t>库随机权重</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -102,6 +102,9 @@
   <si>
     <t>700000001,700010101,700010102,700010112,700010122,700010132,700010103,700010104,700010105,700010106,700010107,700010108,700100001,700100101,700100102,700100112,700100122,700100132,700100103,700100104,700100105,700100106,700100107,700100108,700200001,700200101,700200102,700200112,700200122,700200132,700200103,700200104,700200105,700200106,700200107,700200108,700400001,700400002,700400003,700400004,700400101,700400102,700400103,700400104,801100101,801100102,801100103</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501,600200001,600200101,600200102,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501</t>
   </si>
 </sst>
 </file>
@@ -524,7 +527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F2A891-7ADB-4315-87EE-F51F4FB85BA3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -891,6 +894,90 @@
         <v>100</v>
       </c>
     </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>401</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>402</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>403</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>404</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>405</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
+        <v>406</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A720D193-2185-40BD-B240-B008B2BB4BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2EEE97D-F857-49DB-BB06-271AA6310122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
@@ -104,7 +104,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501,600200001,600200101,600200102,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501</t>
+    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501,600200001,600200101,600200102,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501,700000001,700010101,700010102,700010112,700010122,700010132,700100001,700100101,700100102,700100112,700100122,700100132</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -180,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -192,6 +193,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -901,7 +903,7 @@
       <c r="B27" s="1">
         <v>0</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="1">
@@ -915,7 +917,7 @@
       <c r="B28" s="1">
         <v>0</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="1">
@@ -929,7 +931,7 @@
       <c r="B29" s="1">
         <v>0</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="1">
@@ -943,7 +945,7 @@
       <c r="B30" s="1">
         <v>0</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="1">
@@ -957,7 +959,7 @@
       <c r="B31" s="1">
         <v>0</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="1">
@@ -971,7 +973,7 @@
       <c r="B32" s="1">
         <v>0</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="1">

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2EEE97D-F857-49DB-BB06-271AA6310122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFFCB86-1B81-4470-96CC-E426DF295D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_library_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="21">
   <si>
     <t>库随机权重</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -104,8 +104,17 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501,600200001,600200101,600200102,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501,700000001,700010101,700010102,700010112,700010122,700010132,700100001,700100101,700100102,700100112,700100122,700100132</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501,600200001,600200101,600200102,600200112,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600300001,600300101,600300102,600300103,600300201,600300202,600300203,600300301,600300302,600300303,600300401,600300501,600400001,600400101,600400102,600400112,600400103,600400201,600400202,600400203,600400301,600400302,600400303,600400401,600400501</t>
+  </si>
+  <si>
+    <t>600500001,600500101,600500102,600500103,600500201,600500202,600500203,600500301,600500302,600500303,600500401,600500501,600600001,600600101,600600102,600600112,600600103,600600201,600600202,600600203,600600301,600600302,600600303,600600401,600600501</t>
+  </si>
+  <si>
+    <t>600700001,600700101,600700102,600700103,600700201,600700202,600700203,600700301,600700302,600700303,600700401,600700501,600800001,600800101,600800102,600800112,600800103,600800201,600800202,600800203,600800301,600800302,600800303,600800401,600800501</t>
   </si>
 </sst>
 </file>
@@ -529,7 +538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F2A891-7ADB-4315-87EE-F51F4FB85BA3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -932,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
@@ -946,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
@@ -960,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
@@ -974,9 +983,37 @@
         <v>0</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D32" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>407</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
+        <v>408</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="1">
         <v>100</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFFCB86-1B81-4470-96CC-E426DF295D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1101C8-4C8D-400E-96A5-45DD31F217DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
   <si>
     <t>库随机权重</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -115,6 +115,10 @@
   </si>
   <si>
     <t>600700001,600700101,600700102,600700103,600700201,600700202,600700203,600700301,600700302,600700303,600700401,600700501,600800001,600800101,600800102,600800112,600800103,600800201,600800202,600800203,600800301,600800302,600800303,600800401,600800501</t>
+  </si>
+  <si>
+    <t>600900001,600900101,600900102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -538,7 +542,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F2A891-7ADB-4315-87EE-F51F4FB85BA3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -1017,6 +1021,20 @@
         <v>100</v>
       </c>
     </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>409</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1101C8-4C8D-400E-96A5-45DD31F217DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EA9D42-7094-4EC9-BE89-BA4A13896427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
   <si>
     <t>库随机权重</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -104,20 +104,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501,600200001,600200101,600200102,600200112,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600300001,600300101,600300102,600300103,600300201,600300202,600300203,600300301,600300302,600300303,600300401,600300501,600400001,600400101,600400102,600400112,600400103,600400201,600400202,600400203,600400301,600400302,600400303,600400401,600400501</t>
-  </si>
-  <si>
-    <t>600500001,600500101,600500102,600500103,600500201,600500202,600500203,600500301,600500302,600500303,600500401,600500501,600600001,600600101,600600102,600600112,600600103,600600201,600600202,600600203,600600301,600600302,600600303,600600401,600600501</t>
-  </si>
-  <si>
-    <t>600700001,600700101,600700102,600700103,600700201,600700202,600700203,600700301,600700302,600700303,600700401,600700501,600800001,600800101,600800102,600800112,600800103,600800201,600800202,600800203,600800301,600800302,600800303,600800401,600800501</t>
-  </si>
-  <si>
     <t>600900001,600900101,600900102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501,600200001,600200101,600200102,600200112,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501,600300001,600300101,600300102,600300103,600300201,600300202,600300203,600300301,600300302,600300303,600300401,600300501,600400001,600400101,600400102,600400112,600400103,600400201,600400202,600400203,600400301,600400302,600400303,600400401,600400501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600500001,600500101,600500102,600500103,600500201,600500202,600500203,600500301,600500302,600500303,600500401,600500501,600600001,600600101,600600102,600600112,600600103,600600201,600600202,600600203,600600301,600600302,600600303,600600401,600600501,600700001,600700101,600700102,600700103,600700201,600700202,600700203,600700301,600700302,600700303,600700401,600700501,600800001,600800101,600800102,600800112,600800103,600800201,600800202,600800203,600800301,600800302,600800303,600800401,600800501</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -917,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D27" s="1">
         <v>100</v>
@@ -931,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
@@ -1000,8 +995,8 @@
       <c r="B33" s="1">
         <v>0</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>20</v>
+      <c r="C33" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
@@ -1014,8 +1009,8 @@
       <c r="B34" s="1">
         <v>0</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>20</v>
+      <c r="C34" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D34" s="1">
         <v>100</v>
@@ -1029,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D35" s="1">
         <v>100</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EA9D42-7094-4EC9-BE89-BA4A13896427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1481462C-9BCB-47BA-9417-6EEAB6E941A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
@@ -37,11 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
-  <si>
-    <t>库随机权重</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
   <si>
     <t>库包括的词条id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -51,10 +47,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>weight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>affix_id_list</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -63,10 +55,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>LIST&lt;INT&gt;_S</t>
   </si>
   <si>
@@ -108,11 +96,59 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501,600200001,600200101,600200102,600200112,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501,600300001,600300101,600300102,600300103,600300201,600300202,600300203,600300301,600300302,600300303,600300401,600300501,600400001,600400101,600400102,600400112,600400103,600400201,600400202,600400203,600400301,600400302,600400303,600400401,600400501</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600500001,600500101,600500102,600500103,600500201,600500202,600500203,600500301,600500302,600500303,600500401,600500501,600600001,600600101,600600102,600600112,600600103,600600201,600600202,600600203,600600301,600600302,600600303,600600401,600600501,600700001,600700101,600700102,600700103,600700201,600700202,600700203,600700301,600700302,600700303,600700401,600700501,600800001,600800101,600800102,600800112,600800103,600800201,600800202,600800203,600800301,600800302,600800303,600800401,600800501</t>
+    <t>600100001,600100101,600100102,600100103,600100201,600100202,600100203,600100301,600100302,600100303,600100401,600100501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600200001,600200101,600200102,600200112,600200103,600200201,600200202,600200203,600200301,600200302,600200303,600200401,600200501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600300001,600300101,600300102,600300103,600300201,600300202,600300203,600300301,600300302,600300303,600300401,600300501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600400001,600400101,600400102,600400112,600400103,600400201,600400202,600400203,600400301,600400302,600400303,600400401,600400501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600500001,600500101,600500102,600500103,600500201,600500202,600500203,600500301,600500302,600500303,600500401,600500501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600600001,600600101,600600102,600600112,600600103,600600201,600600202,600600203,600600301,600600302,600600303,600600401,600600501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600800001,600800101,600800102,600800112,600800103,600800201,600800202,600800203,600800301,600800302,600800303,600800401,600800501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600700001,600700101,600700102,600700103,600700201,600700202,600700203,600700301,600700302,600700303,600700401,600700501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000,10000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>库词条已选次数影响权重系数（加值\万分比）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>库已随次数影响权重系数（减值\万分比）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>weight_adjust1_add</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>weight_adjust2_sub</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000,6000,7000,8000,9000,10000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -189,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -202,6 +238,12 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -537,66 +579,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F2A891-7ADB-4315-87EE-F51F4FB85BA3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="105.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -604,13 +656,14 @@
         <v>0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -618,13 +671,14 @@
         <v>0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -632,13 +686,14 @@
         <v>0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -646,13 +701,14 @@
         <v>0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -660,13 +716,14 @@
         <v>0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>101</v>
       </c>
@@ -674,13 +731,14 @@
         <v>0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>102</v>
       </c>
@@ -688,13 +746,14 @@
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>103</v>
       </c>
@@ -702,13 +761,14 @@
         <v>0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>104</v>
       </c>
@@ -716,13 +776,14 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>105</v>
       </c>
@@ -730,13 +791,14 @@
         <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -744,13 +806,14 @@
         <v>10109011</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -758,13 +821,14 @@
         <v>10109012</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>201</v>
       </c>
@@ -772,13 +836,14 @@
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>202</v>
       </c>
@@ -786,13 +851,14 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>203</v>
       </c>
@@ -800,13 +866,14 @@
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>204</v>
       </c>
@@ -814,13 +881,14 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>205</v>
       </c>
@@ -828,13 +896,14 @@
         <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>301</v>
       </c>
@@ -842,13 +911,14 @@
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>302</v>
       </c>
@@ -856,13 +926,14 @@
         <v>0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>303</v>
       </c>
@@ -870,13 +941,14 @@
         <v>0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>304</v>
       </c>
@@ -884,13 +956,14 @@
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>305</v>
       </c>
@@ -898,13 +971,14 @@
         <v>0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+      <c r="D26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>401</v>
       </c>
@@ -912,13 +986,16 @@
         <v>0</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+        <v>15</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>402</v>
       </c>
@@ -926,13 +1003,16 @@
         <v>0</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>403</v>
       </c>
@@ -940,13 +1020,16 @@
         <v>0</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>404</v>
       </c>
@@ -956,11 +1039,14 @@
       <c r="C30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="D30" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>405</v>
       </c>
@@ -970,11 +1056,14 @@
       <c r="C31" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="D31" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>406</v>
       </c>
@@ -982,13 +1071,16 @@
         <v>0</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>407</v>
       </c>
@@ -996,13 +1088,16 @@
         <v>0</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+        <v>22</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>408</v>
       </c>
@@ -1010,13 +1105,16 @@
         <v>0</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>409</v>
       </c>
@@ -1024,10 +1122,13 @@
         <v>0</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="1">
-        <v>100</v>
+        <v>14</v>
+      </c>
+      <c r="D35" s="8">
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1481462C-9BCB-47BA-9417-6EEAB6E941A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C87E44C-FC93-4AFC-8546-470192DE9B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
@@ -132,14 +132,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>库词条已选次数影响权重系数（加值\万分比）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>库已随次数影响权重系数（减值\万分比）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>weight_adjust1_add</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -149,6 +141,14 @@
   </si>
   <si>
     <t>5000,6000,7000,8000,9000,10000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>库词条已选次数影响权重系数（加值，万分比）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>库已随次数影响权重系数（减值，万分比）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -625,10 +625,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
@@ -989,7 +989,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>23</v>
@@ -1006,7 +1006,7 @@
         <v>16</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>23</v>
@@ -1023,7 +1023,7 @@
         <v>17</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>23</v>
@@ -1040,7 +1040,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>23</v>
@@ -1057,7 +1057,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>23</v>
@@ -1074,7 +1074,7 @@
         <v>20</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>23</v>
@@ -1091,7 +1091,7 @@
         <v>22</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>23</v>
@@ -1108,7 +1108,7 @@
         <v>21</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>23</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C87E44C-FC93-4AFC-8546-470192DE9B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE260430-0443-45B5-A40D-F2D5B5D61F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
@@ -140,15 +140,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>5000,6000,7000,8000,9000,10000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>库词条已选次数影响权重系数（加值，万分比）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>库已随次数影响权重系数（减值，万分比）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000,15000,20000,22500,25000,27500,30000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
@@ -989,7 +989,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>23</v>
@@ -1006,7 +1006,7 @@
         <v>16</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>23</v>
@@ -1023,7 +1023,7 @@
         <v>17</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>23</v>
@@ -1040,7 +1040,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>23</v>
@@ -1057,7 +1057,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>23</v>
@@ -1074,7 +1074,7 @@
         <v>20</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>23</v>
@@ -1091,7 +1091,7 @@
         <v>22</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>23</v>
@@ -1108,7 +1108,7 @@
         <v>21</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>23</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE260430-0443-45B5-A40D-F2D5B5D61F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4C2D6C-675A-45D8-B5C0-033EFE344624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_library_v8" sheetId="1" r:id="rId1"/>
@@ -148,7 +148,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>10000,15000,20000,22500,25000,27500,30000</t>
+    <t>12500,15000,17500,20000,22000,24000,25000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_library_v8【迷宫-能量词条库权重】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4C2D6C-675A-45D8-B5C0-033EFE344624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB024347-319A-499F-BC0F-7E6C3FB80E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4E2A6-24F2-41C3-89AA-27E48F1F443E}"/>
   </bookViews>
@@ -148,7 +148,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>12500,15000,17500,20000,22000,24000,25000</t>
+    <t>12000,13500,15000,16500,18000,19000,20000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
